--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260611.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.94%</t>
+          <t>12.10%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.53%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.97%</t>
+          <t>9.11%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.18%</t>
+          <t>7.30%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>5.40%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.63%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>SWX US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>西南天然氣控股公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>65,675</t>
+          <t>21,103</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>SWX US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>西南天然氣控股公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>21,103</t>
+          <t>65,675</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1056,73 +1056,73 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>34,552</t>
+          <t>54,509</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>54,509</t>
+          <t>34,552</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>53,140</t>
+          <t>14,428</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1151,22 +1151,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>31,595</t>
+          <t>53,140</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1188,46 +1188,46 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,428</t>
+          <t>31,595</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>41,875</t>
+          <t>11,297</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,22 +1239,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>11,297</t>
+          <t>41,875</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1320,46 +1320,46 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>202606ESM6</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15,450</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>202606ESM6</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>14,674</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,22 +1371,22 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>15,450</t>
+          <t>14,674</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1430,51 +1430,51 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>ENPH US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>Enphase能源公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>16,932</t>
+          <t>31,476</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>ENPH US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Enphase能源公司</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>31,476</t>
+          <t>16,932</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1518,51 +1518,51 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>18,188</t>
+          <t>77,540</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>77,540</t>
+          <t>18,188</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.02%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>163,711,409</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
